--- a/templates/fr24-sablon.xlsx
+++ b/templates/fr24-sablon.xlsx
@@ -2390,6 +2390,19 @@
         <v>108</v>
       </c>
       <c r="F16" s="30"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Çalışmayı yapan</t>
+        </is>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
@@ -3316,7 +3329,9 @@
       <c r="D74" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="82">
+  <mergeCells count="84">
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="N16:R16"/>
     <mergeCell ref="N41:R41"/>
     <mergeCell ref="J45:R45"/>
     <mergeCell ref="J18:M18"/>
